--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10951.47</v>
+        <v>10835.01</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18624.4</v>
+        <v>18426.35</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8945.25</v>
+        <v>8785.35</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29271.95</v>
+        <v>28748.7</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10585.99</v>
+        <v>10396.76</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>31362.8</v>
+        <v>30970.65</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>46450.67</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>41367.42</v>
+        <v>41437.2</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46450.67</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7262.67</v>
+        <v>7274.93</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>497645.55</v>
+        <v>498484.99</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38885.37</v>
+        <v>38950.97</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>32520.19</v>
+        <v>32773.79</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13880.57</v>
+        <v>13988.81</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>36616.27</v>
+        <v>36901.82</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>23288.76</v>
+        <v>23470.38</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25458.95</v>
+        <v>25657.49</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>53523.59</v>
+        <v>53958.89</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>36564.84</v>
+        <v>36761.26</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7335.41</v>
+        <v>7350.17</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12714.27</v>
+        <v>12739.84</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>61554.72</v>
+        <v>61316.16</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13242.07</v>
+        <v>13190.75</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7340.6</v>
+        <v>7312.15</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>105900.59</v>
+        <v>105490.17</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>34101.14</v>
+        <v>33968.98</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8796.709999999999</v>
+        <v>8857.620000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12911.13</v>
+        <v>13000.53</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>592589.62</v>
+        <v>587107.27</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8530.68</v>
+        <v>8451.76</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>65236.42</v>
+        <v>65024.86</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>360947.33</v>
+        <v>357020.86</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7335.96</v>
+        <v>7267.5</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>40126.4</v>
+        <v>40131.31</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>42814.45</v>
+        <v>42819.69</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>22662.15</v>
+        <v>22688.73</v>
       </c>
     </row>
     <row r="38">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1641207.55</v>
+        <v>1643132.54</v>
       </c>
     </row>
     <row r="39">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32810.58</v>
+        <v>33105.94</v>
       </c>
     </row>
     <row r="40">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>313385.18</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="41">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18606.27</v>
+        <v>18773.77</v>
       </c>
     </row>
     <row r="42">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>57252.51</v>
+        <v>57700.25</v>
       </c>
     </row>
     <row r="43">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>63400.07</v>
+        <v>63895.88</v>
       </c>
     </row>
     <row r="44">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>70936.44</v>
+        <v>71491.19</v>
       </c>
     </row>
     <row r="45">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>13893.3</v>
+        <v>14001.95</v>
       </c>
     </row>
     <row r="46">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13590.55</v>
+        <v>13696.83</v>
       </c>
     </row>
     <row r="47">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>11029.98</v>
+        <v>11116.24</v>
       </c>
     </row>
     <row r="48">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11499.69</v>
+        <v>11589.63</v>
       </c>
     </row>
     <row r="49">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>56632</v>
+        <v>57074.88</v>
       </c>
     </row>
     <row r="50">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>49640.9</v>
+        <v>50043.25</v>
       </c>
     </row>
     <row r="51">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>108751.26</v>
+        <v>109632.69</v>
       </c>
     </row>
     <row r="52">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>28223.23</v>
+        <v>28451.98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Asimov Consultores SpA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LAHUEN HEALTH SERVICES SPA</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -636,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1588-83-CM26</t>
+          <t>2345-73-SE26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,12 +665,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,28 +680,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>COMILLAS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>77.714.554-1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8785.35</v>
+        <v>287573.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1191449-55-CM26</t>
+          <t>1588-83-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,12 +730,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +745,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +760,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>28748.7</v>
+        <v>8785.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5627-111-CM26</t>
+          <t>1191449-55-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,12 +791,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10396.76</v>
+        <v>28748.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2341-184-CM26</t>
+          <t>5627-111-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +852,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +867,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30970.65</v>
+        <v>10396.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1704-2534-CM26</t>
+          <t>2341-184-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +907,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,27 +917,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +947,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>46529.02</v>
+        <v>30970.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1725-309-CM26</t>
+          <t>1704-2535-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +973,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +993,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +1008,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>41437.2</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1704-2535-CM26</t>
+          <t>1725-309-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1034,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1054,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1069,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46529.02</v>
+        <v>41437.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>359-1280-SE26</t>
+          <t>1704-2534-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,47 +1100,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.608.404-6</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Instituto Nacional del Cancer</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Lahuen Health Services SpA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.227.643-7</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.616.770-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7274.93</v>
+        <v>46529.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>730566-40-CM26</t>
+          <t>359-1280-SE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1148,17 +1156,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.608.404-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>Instituto Nacional del Cancer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1176,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>Lahuen Health Services SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.227.643-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>498484.99</v>
+        <v>7274.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5586-1200-CM26</t>
+          <t>730566-40-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1209,32 +1221,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1256,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38950.97</v>
+        <v>498484.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>622844-15-CM26</t>
+          <t>5586-1200-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,53 +1277,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>32773.79</v>
+        <v>38950.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4517-8-CM26</t>
+          <t>622844-15-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,13 +1382,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13988.81</v>
+        <v>32773.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3447-1226-CM26</t>
+          <t>4517-8-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,32 +1408,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1443,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>36901.82</v>
+        <v>13988.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2674-407-CM26</t>
+          <t>3447-1226-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1453,48 +1469,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>23470.38</v>
+        <v>36901.82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2291-780-CM26</t>
+          <t>2674-407-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1519,27 +1539,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1569,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25657.49</v>
+        <v>23470.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2378-90-CM26</t>
+          <t>2291-780-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,37 +1590,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1630,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>53958.89</v>
+        <v>25657.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2793-414-CM26</t>
+          <t>2378-90-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1651,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1661,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,28 +1676,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>36761.26</v>
+        <v>53958.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2766-212-CM26</t>
+          <t>2793-414-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1716,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1726,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,28 +1741,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7350.17</v>
+        <v>36761.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>812799-115-CM26</t>
+          <t>2766-212-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1763,43 +1791,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12739.84</v>
+        <v>7350.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1177296-173-CM26</t>
+          <t>812799-115-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1814,7 +1846,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,27 +1856,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1886,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>61316.16</v>
+        <v>12739.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>759-104-CM26</t>
+          <t>1177296-173-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1880,17 +1912,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,28 +1932,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13190.75</v>
+        <v>61316.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1480134-17-CM26</t>
+          <t>759-104-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,17 +1977,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,28 +1997,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ANIDA CONSULTORES S A</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.680.090-2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.092.019-3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7312.15</v>
+        <v>13190.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1005498-52-CM26</t>
+          <t>1480134-17-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2002,17 +2042,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2062,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
+          <t>ANIDA CONSULTORES S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.489.853-2</t>
+          <t>77.680.090-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2077,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>105490.17</v>
+        <v>7312.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>756-66-CM26</t>
+          <t>1005498-52-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2068,12 +2108,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>60.810.000-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2123,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>INFO-UPDATE LIMITADA</t>
+          <t>SOLUCIONES TECNOLÓGICAS COORDENADA SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.023.530-k</t>
+          <t>76.489.853-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2138,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>33968.98</v>
+        <v>105490.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2734-283-CM26</t>
+          <t>756-66-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,22 +2159,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2184,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>INFO-UPDATE LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.023.530-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2199,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8857.620000000001</v>
+        <v>33968.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2387-222-CM26</t>
+          <t>2734-283-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2190,27 +2230,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2260,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>13000.53</v>
+        <v>8857.620000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1750-120-CM26</t>
+          <t>2387-222-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,53 +2281,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.290.590-0</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>587107.27</v>
+        <v>13000.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1036569-66-CM26</t>
+          <t>1750-120-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2307,48 +2351,52 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>65.290.590-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>DIRECCION NACIONAL DEL SERVICIO CIVIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8451.76</v>
+        <v>587107.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1111089-140-CM26</t>
+          <t>1036569-66-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,7 +2411,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,27 +2421,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2451,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>65024.86</v>
+        <v>8451.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1415862-28-SE26</t>
+          <t>1111089-140-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,22 +2472,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2497,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2468,13 +2516,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>357020.86</v>
+        <v>65024.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2664-398-CM26</t>
+          <t>520149-65-SE26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2494,48 +2542,52 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.150.102-7</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>ALTAVOZ SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>96.827.350-7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7267.5</v>
+        <v>30688.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4610-30-CM26</t>
+          <t>1415862-28-SE26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2550,7 +2602,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2560,43 +2612,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>40131.31</v>
+        <v>357020.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4301-323-CM26</t>
+          <t>2664-398-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2611,7 +2667,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2621,43 +2677,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.150.102-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>42819.69</v>
+        <v>7267.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1588-88-SE26</t>
+          <t>4610-30-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2672,7 +2732,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,43 +2742,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>22688.73</v>
+        <v>40131.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>591-155-SE26</t>
+          <t>4301-323-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2733,7 +2797,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,27 +2807,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ANTICIPA S A</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.771.610-3</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2777,13 +2841,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1643132.54</v>
+        <v>42819.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>463-27-CM26</t>
+          <t>1588-88-SE26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2798,22 +2862,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2823,12 +2887,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>ACS INGENIEROS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>76.240.927-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2838,13 +2902,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>33105.94</v>
+        <v>22688.73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1177296-550-CM25</t>
+          <t>591-155-SE26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2859,22 +2923,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2884,28 +2948,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>ANTICIPA S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>96.771.610-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>316206.29</v>
+        <v>1643132.54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5768-77-CM26</t>
+          <t>709603-98-SE26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2930,12 +2998,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,28 +3013,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>XMS Business Solutions S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.249.938-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18773.77</v>
+        <v>8670.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1655-148-CM26</t>
+          <t>463-27-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2981,7 +3053,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,12 +3063,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,28 +3078,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>57700.25</v>
+        <v>33105.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2268-87-CM26</t>
+          <t>1177296-550-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3042,22 +3118,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,12 +3143,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TBUSINESS SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.009.886-6</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,13 +3158,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>63895.88</v>
+        <v>316206.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>599-82-CM26</t>
+          <t>5768-77-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3103,7 +3179,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3113,12 +3189,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3128,28 +3204,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>71491.19</v>
+        <v>18773.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2766-277-CM26</t>
+          <t>1655-148-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3174,12 +3254,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,28 +3269,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>14001.95</v>
+        <v>57700.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3708-183-CM26</t>
+          <t>2268-87-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3235,27 +3319,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>TBUSINESS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>77.009.886-6</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3265,13 +3349,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13696.83</v>
+        <v>63895.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2083-1-CM26</t>
+          <t>599-82-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3296,12 +3380,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3311,28 +3395,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>11116.24</v>
+        <v>71491.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5627-131-CM26</t>
+          <t>2766-277-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3357,12 +3445,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,28 +3460,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11589.63</v>
+        <v>14001.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5574-43-CM26</t>
+          <t>3708-183-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3418,43 +3510,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>57074.88</v>
+        <v>13696.83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1305552-66-CM26</t>
+          <t>2083-1-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3469,53 +3565,57 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.981.030-9</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Andestic SpA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>50043.25</v>
+        <v>11116.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>599-58-CM26</t>
+          <t>5627-131-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3530,22 +3630,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3555,12 +3655,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,67 +3670,262 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>109632.69</v>
+        <v>11589.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>5574-43-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>57074.88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1305552-66-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.981.030-9</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Andestic SpA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.031.392-0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>50043.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>599-58-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>109632.69</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>1469-1393-CM26</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>70.885.500-6</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="n">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
         <v>28451.98</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -1001,7 +1001,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1123,7 +1127,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3151,7 +3159,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/may-2026.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
